--- a/week-02/Ex2A_events_normalized.xlsx
+++ b/week-02/Ex2A_events_normalized.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thaniastaana\DataAnalytics\week-02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C5010618-E169-4EE7-A155-65F52066D324}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{30162C28-0799-4651-A68D-F274EF9FFA28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6996" yWindow="2352" windowWidth="14844" windowHeight="9636" xr2:uid="{5091876E-AF08-41C4-B976-D2AB9D8B455C}"/>
+    <workbookView xWindow="4080" yWindow="2400" windowWidth="14844" windowHeight="9636" xr2:uid="{5091876E-AF08-41C4-B976-D2AB9D8B455C}"/>
   </bookViews>
   <sheets>
     <sheet name="events_sample" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="147">
   <si>
     <t>Event ID</t>
   </si>
@@ -471,6 +471,9 @@
   </si>
   <si>
     <t>Venue ID (FK)</t>
+  </si>
+  <si>
+    <t>My CoPilot said my tables were all good</t>
   </si>
 </sst>
 </file>
@@ -1369,7 +1372,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FA38BEC-78EC-44DC-83F3-AA711D021920}">
-  <dimension ref="A1:Q71"/>
+  <dimension ref="A1:Q74"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.33203125" customWidth="1"/>
@@ -2519,7 +2522,7 @@
       <c r="C61" t="s">
         <v>3</v>
       </c>
-      <c r="D61">
+      <c r="D61" s="1">
         <v>46095</v>
       </c>
       <c r="E61">
@@ -2539,7 +2542,7 @@
       <c r="C62" t="s">
         <v>7</v>
       </c>
-      <c r="D62">
+      <c r="D62" s="1">
         <v>46194</v>
       </c>
       <c r="E62">
@@ -2559,7 +2562,7 @@
       <c r="C63" t="s">
         <v>10</v>
       </c>
-      <c r="D63">
+      <c r="D63" s="1">
         <v>46115</v>
       </c>
       <c r="E63">
@@ -2579,7 +2582,7 @@
       <c r="C64" t="s">
         <v>14</v>
       </c>
-      <c r="D64">
+      <c r="D64" s="1">
         <v>46157</v>
       </c>
       <c r="E64">
@@ -2592,14 +2595,14 @@
         <v>118</v>
       </c>
     </row>
-    <row r="65" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B65">
         <v>106</v>
       </c>
       <c r="C65" t="s">
         <v>17</v>
       </c>
-      <c r="D65">
+      <c r="D65" s="1">
         <v>46109</v>
       </c>
       <c r="E65">
@@ -2612,14 +2615,14 @@
         <v>119</v>
       </c>
     </row>
-    <row r="66" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B66">
         <v>107</v>
       </c>
       <c r="C66" t="s">
         <v>21</v>
       </c>
-      <c r="D66">
+      <c r="D66" s="1">
         <v>46130</v>
       </c>
       <c r="E66">
@@ -2632,14 +2635,14 @@
         <v>118</v>
       </c>
     </row>
-    <row r="67" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B67">
         <v>108</v>
       </c>
       <c r="C67" t="s">
         <v>24</v>
       </c>
-      <c r="D67">
+      <c r="D67" s="1">
         <v>46144</v>
       </c>
       <c r="E67">
@@ -2652,14 +2655,14 @@
         <v>120</v>
       </c>
     </row>
-    <row r="68" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B68">
         <v>109</v>
       </c>
       <c r="C68" t="s">
         <v>27</v>
       </c>
-      <c r="D68">
+      <c r="D68" s="1">
         <v>46181</v>
       </c>
       <c r="E68">
@@ -2672,14 +2675,14 @@
         <v>121</v>
       </c>
     </row>
-    <row r="69" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B69">
         <v>110</v>
       </c>
       <c r="C69" t="s">
         <v>30</v>
       </c>
-      <c r="D69">
+      <c r="D69" s="1">
         <v>46215</v>
       </c>
       <c r="E69">
@@ -2692,14 +2695,14 @@
         <v>116</v>
       </c>
     </row>
-    <row r="70" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B70">
         <v>111</v>
       </c>
       <c r="C70" t="s">
         <v>31</v>
       </c>
-      <c r="D70">
+      <c r="D70" s="1">
         <v>46102</v>
       </c>
       <c r="E70">
@@ -2712,14 +2715,14 @@
         <v>122</v>
       </c>
     </row>
-    <row r="71" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B71">
         <v>112</v>
       </c>
       <c r="C71" t="s">
         <v>33</v>
       </c>
-      <c r="D71">
+      <c r="D71" s="1">
         <v>46137</v>
       </c>
       <c r="E71">
@@ -2730,6 +2733,11 @@
       </c>
       <c r="G71" t="s">
         <v>123</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -2749,26 +2757,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="ced60a7f-99b1-48d2-b555-34851c8026ae" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9e0b35a9-e6cb-436b-81d4-4440ba439ca5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100CA5D0A6329BB324E86983B32928CFC2E" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3d7eac4bce3bbb09c82bd908806be82e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9e0b35a9-e6cb-436b-81d4-4440ba439ca5" xmlns:ns3="ced60a7f-99b1-48d2-b555-34851c8026ae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="eb51570e5b7cb8bd524bc2df5324d4a3" ns2:_="" ns3:_="">
     <xsd:import namespace="9e0b35a9-e6cb-436b-81d4-4440ba439ca5"/>
@@ -3009,26 +2997,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EE6EC55-B0E7-4ACE-A5DA-E03DCA4973DE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ced60a7f-99b1-48d2-b555-34851c8026ae"/>
-    <ds:schemaRef ds:uri="9e0b35a9-e6cb-436b-81d4-4440ba439ca5"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D48FB9E6-6DE3-40FB-81F7-677295638F7C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="ced60a7f-99b1-48d2-b555-34851c8026ae" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9e0b35a9-e6cb-436b-81d4-4440ba439ca5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6414E68-BBC1-4A96-B078-EF7EE95D29CE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3045,4 +3034,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D48FB9E6-6DE3-40FB-81F7-677295638F7C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EE6EC55-B0E7-4ACE-A5DA-E03DCA4973DE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ced60a7f-99b1-48d2-b555-34851c8026ae"/>
+    <ds:schemaRef ds:uri="9e0b35a9-e6cb-436b-81d4-4440ba439ca5"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>